--- a/resources/templates/standard/H2100-03.xlsx
+++ b/resources/templates/standard/H2100-03.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="38">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>일일 납품실적 보고서 (       반)</t>
   </si>
@@ -944,11 +947,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -969,20 +974,20 @@
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE1" s="4"/>
       <c r="AF1" s="4"/>
@@ -1066,7 +1071,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1087,7 +1092,7 @@
       <c r="R4" s="5"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
@@ -1107,7 +1112,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -1124,7 +1129,7 @@
       <c r="N5" s="10"/>
       <c r="O5" s="10"/>
       <c r="P5" s="11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
@@ -1141,7 +1146,7 @@
       <c r="AC5" s="11"/>
       <c r="AD5" s="11"/>
       <c r="AE5" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF5" s="12"/>
       <c r="AG5" s="5"/>
@@ -1150,52 +1155,52 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
       <c r="D6" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="14"/>
       <c r="G6" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="J6" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6" s="14"/>
       <c r="L6" s="14"/>
       <c r="M6" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
       <c r="P6" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="14"/>
       <c r="S6" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
       <c r="V6" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W6" s="14"/>
       <c r="X6" s="14"/>
       <c r="Y6" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z6" s="14"/>
       <c r="AA6" s="14"/>
       <c r="AB6" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC6" s="14"/>
       <c r="AD6" s="14"/>
@@ -1207,57 +1212,57 @@
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
       <c r="J7" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
       <c r="M7" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
       <c r="P7" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q7" s="16"/>
       <c r="R7" s="16"/>
       <c r="S7" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T7" s="16"/>
       <c r="U7" s="16"/>
       <c r="V7" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W7" s="16"/>
       <c r="X7" s="16"/>
       <c r="Y7" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z7" s="16"/>
       <c r="AA7" s="16"/>
       <c r="AB7" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC7" s="17"/>
       <c r="AD7" s="17"/>
       <c r="AE7" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF7" s="18"/>
       <c r="AG7" s="5"/>
@@ -1266,52 +1271,52 @@
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
       <c r="D8" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
       <c r="G8" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" s="20"/>
       <c r="I8" s="20"/>
       <c r="J8" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
       <c r="M8" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N8" s="21"/>
       <c r="O8" s="21"/>
       <c r="P8" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q8" s="20"/>
       <c r="R8" s="20"/>
       <c r="S8" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T8" s="20"/>
       <c r="U8" s="20"/>
       <c r="V8" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W8" s="20"/>
       <c r="X8" s="20"/>
       <c r="Y8" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z8" s="20"/>
       <c r="AA8" s="20"/>
       <c r="AB8" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC8" s="21"/>
       <c r="AD8" s="21"/>
@@ -1323,7 +1328,7 @@
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1340,27 +1345,27 @@
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
       <c r="P9" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q9" s="22"/>
       <c r="R9" s="22"/>
       <c r="S9" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T9" s="22"/>
       <c r="U9" s="22"/>
       <c r="V9" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W9" s="22"/>
       <c r="X9" s="22"/>
       <c r="Y9" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z9" s="22"/>
       <c r="AA9" s="22"/>
       <c r="AB9" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC9" s="23"/>
       <c r="AD9" s="23"/>
@@ -1386,7 +1391,7 @@
       <c r="M10" s="24"/>
       <c r="N10" s="26"/>
       <c r="O10" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P10" s="27"/>
       <c r="Q10" s="27"/>
@@ -1397,7 +1402,7 @@
       <c r="V10" s="28"/>
       <c r="W10" s="28"/>
       <c r="X10" s="29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y10" s="29"/>
       <c r="Z10" s="29"/>
@@ -1450,7 +1455,7 @@
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
@@ -1486,36 +1491,36 @@
       <c r="AG12" s="5"/>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="33"/>
       <c r="C13" s="34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="34"/>
       <c r="I13" s="34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J13" s="34"/>
       <c r="K13" s="34"/>
       <c r="L13" s="35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M13" s="35"/>
       <c r="N13" s="35"/>
       <c r="O13" s="34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P13" s="34"/>
       <c r="Q13" s="34"/>
@@ -1524,16 +1529,16 @@
       <c r="T13" s="34"/>
       <c r="U13" s="34"/>
       <c r="V13" s="34" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W13" s="34"/>
       <c r="X13" s="34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y13" s="34"/>
       <c r="Z13" s="34"/>
       <c r="AA13" s="34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AB13" s="34"/>
       <c r="AC13" s="34"/>
@@ -1543,7 +1548,7 @@
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
@@ -1556,40 +1561,40 @@
       <c r="G14" s="34"/>
       <c r="H14" s="34"/>
       <c r="I14" s="34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" s="34"/>
       <c r="K14" s="36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L14" s="35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M14" s="35"/>
       <c r="N14" s="37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O14" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P14" s="34"/>
       <c r="Q14" s="34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R14" s="34"/>
       <c r="S14" s="35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T14" s="35"/>
       <c r="U14" s="35"/>
       <c r="V14" s="34"/>
       <c r="W14" s="34"/>
       <c r="X14" s="34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y14" s="34"/>
       <c r="Z14" s="34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA14" s="34"/>
       <c r="AB14" s="34"/>
@@ -1936,7 +1941,7 @@
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="50" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" s="50"/>
       <c r="C24" s="50"/>
@@ -1975,7 +1980,7 @@
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B25" s="60"/>
       <c r="C25" s="60"/>
